--- a/data/trans_orig/IP07A13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>32809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>48555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65566</t>
+          <t>66268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87772</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72411</t>
+          <t>70355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95871</t>
+          <t>93863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144231</t>
+          <t>144491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>176084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91222</t>
+          <t>90754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114252</t>
+          <t>113965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118853</t>
+          <t>120957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>144822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218029</t>
+          <t>216539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251898</t>
+          <t>249823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54405</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>37993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55798</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54865</t>
+          <t>54528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73215</t>
+          <t>73117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>112011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115134</t>
+          <t>114200</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142308</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273662</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141788</t>
+          <t>143450</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>171510</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>166959</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>194767</t>
+          <t>197175</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317405</t>
+          <t>319018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>361235</t>
+          <t>359750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>21591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>43566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58975</t>
+          <t>59517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>75891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80455</t>
+          <t>80517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104475</t>
+          <t>105495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141144</t>
+          <t>141835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173619</t>
+          <t>174337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106825</t>
+          <t>107730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129795</t>
+          <t>130062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>96649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122171</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210468</t>
+          <t>210952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245620</t>
+          <t>245081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>44194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>19887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>56088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72881</t>
+          <t>73143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117215</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>115467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143773</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214992</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254501</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169633</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>198426</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>145291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171993</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>321210</t>
+          <t>322979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>363247</t>
+          <t>364575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70958</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23290</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>39830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110148</t>
+          <t>107454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136295</t>
+          <t>134443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120487</t>
+          <t>122632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147961</t>
+          <t>148002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239377</t>
+          <t>237564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277790</t>
+          <t>276520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94479</t>
+          <t>97396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120477</t>
+          <t>123196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>76840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101527</t>
+          <t>101494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178028</t>
+          <t>178288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214120</t>
+          <t>215132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>43885</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>43099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67438</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87650</t>
+          <t>86728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>25236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>74638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>157612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190398</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176908</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>209545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390059</t>
+          <t>390229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>171255</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154751</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>270164</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313949</t>
+          <t>315585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21030</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15674</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26644</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25404</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20214</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31269</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19486</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31451</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21030</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14970</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26225</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54336</t>
+          <t>53737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21517</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27344</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13689</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24214</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13307</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23787</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21517</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15837</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27119</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48555</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5247</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4683</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9223</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3452</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83314</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72378</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95263</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>76515</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>66268</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88099</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>64769</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>87849</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>83314</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>70355</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>93863</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,01%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>143172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176084</t>
+          <t>175537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118917</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>143687</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>102592</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90754</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113965</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90820</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114430</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>50,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132004</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>120957</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>144822</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,47%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216539</t>
+          <t>217636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249823</t>
+          <t>250347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -1630,107 +1630,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21316</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29066</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22902</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16889</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31244</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16398</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30220</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15391</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>29783</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>44218</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>35040</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>55178</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>12,52%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>44218</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>35625</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>54876</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3521</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4510</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23741</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17958</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29956</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>23280</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17518</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29997</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17053</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30073</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23741</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17413</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30029</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37993</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>56162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27505</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21573</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33663</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>36443</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29748</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>43041</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>29313</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42748</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>55,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27505</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21367</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34138</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,54%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73117</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7627</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12905</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6411</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11191</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11965</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7627</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12746</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5333</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1521</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4672</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5212</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66134</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66134</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66134</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>128085</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>113629</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>141825</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>37,06%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>32,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>125200</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>112011</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>140390</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>112828</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>140096</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>39,27%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>128085</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>114200</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>142672</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>37,06%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235384</t>
+          <t>233572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275696</t>
+          <t>274572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>181026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>167439</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>197448</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>48,45%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>157742</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>143450</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>172180</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>142912</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>171787</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>49,48%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>181026</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>167474</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>197175</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319018</t>
+          <t>319367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>359750</t>
+          <t>359381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25449</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>44275</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>34560</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>43078</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>26775</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>44395</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>33626</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>25175</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>43263</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>82307</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5934</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3679</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2216</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5859</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3225,87 +3225,87 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>473</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>318795</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>318795</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>318795</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15868</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10762</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21743</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19148</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13827</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24857</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13927</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25994</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15868</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10630</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21591</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>42892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23549</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17934</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29365</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27363</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21589</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32943</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21129</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33150</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>52,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17813</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29224</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59517</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3832</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2524</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9571</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1344</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4086</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45246</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45246</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45246</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45246</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45246</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92644</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80468</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>104503</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>65044</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54348</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75891</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54181</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76675</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>92644</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>80517</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105495</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141835</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174337</t>
+          <t>174113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109692</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122592</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>118432</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107730</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130062</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105848</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129599</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>109692</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96649</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>121822</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210952</t>
+          <t>211356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245081</t>
+          <t>244806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19619</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12851</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16071</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10776</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23898</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23457</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19619</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13375</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27226</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26510</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44304</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7467</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4820,67 +4820,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6260</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6122</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226655</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226655</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226655</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>201964</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>201964</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>201964</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226655</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226655</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20781</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27012</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19626</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13841</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25974</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26158</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>22,1%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20781</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14833</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27271</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,87%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>25,6%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>32088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26415</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20557</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>38073</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31189</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>44194</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>31484</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>44268</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>60,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26415</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19887</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32660</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56088</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,36%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8734</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13777</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8528</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,75%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8734</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5032</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -5384,72 +5384,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>701</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3980</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4435</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5207</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>62628</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>62628</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>62628</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>129293</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>115443</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>144200</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>43,72%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>103819</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>88851</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>116629</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>90670</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>117660</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>32,82%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>129293</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>115467</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>39,2%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214694</t>
+          <t>215100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253258</t>
+          <t>253866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>145424</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>174701</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>52,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>183869</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>169586</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>198595</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>168599</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>197982</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>58,13%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,62%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>62,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>159655</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>145291</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>174990</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>322979</t>
+          <t>321600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>364575</t>
+          <t>361609</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>33575</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25052</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>42934</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>24132</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17422</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>32626</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17801</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>33519</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>33575</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>25122</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>42840</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70073</t>
+          <t>70390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2720</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6161</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -6184,67 +6184,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5403</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4686</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>449</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>316280</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>316280</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>316280</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17128</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12396</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22195</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15601</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10865</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20373</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10617</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20214</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17128</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12380</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22361</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18276</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13067</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22837</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14714</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10023</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19514</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10231</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19471</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>46,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18276</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>39378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -6871,67 +6871,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>1498</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4378</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>135215</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121704</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>147901</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>121967</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>107454</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>134443</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>109378</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>134835</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135215</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122632</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>148002</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237564</t>
+          <t>239243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276520</t>
+          <t>275193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87901</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75625</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100829</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>109055</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123196</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>94871</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121577</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>43,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87901</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76840</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178288</t>
+          <t>180153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215132</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19634</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27329</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14605</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9305</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21679</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8844</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21525</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19634</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13642</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27354</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3294</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7207</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7481</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3649</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7774,92 +7774,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1638</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4967</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>244064</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>244064</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>244064</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>244064</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>244064</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>244064</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41260</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33301</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48302</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36092</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29357</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43099</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28963</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43508</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41260</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34094</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48289</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>67183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86728</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25498</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40035</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>31255</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24530</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38260</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24225</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>42,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>32218</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25236</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40190</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74638</t>
+          <t>73125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3295</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7217</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6388</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3313</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11465</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3112</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11123</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,66%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7462</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3736</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>671</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>73736</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>73736</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>73736</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>77444</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>77444</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>77444</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>193604</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>176521</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>208835</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,31%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>173661</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>157612</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>187861</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>158335</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>190086</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>48,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>193604</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>179298</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>209545</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342511</t>
+          <t>346473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390229</t>
+          <t>389391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>138395</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>122961</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>154049</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>155025</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>140888</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>139404</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>169624</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>43,53%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,56%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>138395</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>123327</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>153934</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272051</t>
+          <t>270380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315585</t>
+          <t>312733</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -8917,67 +8917,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>24162</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>17269</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>33570</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>22491</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>15796</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>30961</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30904</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>6,32%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>24162</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>17189</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>32664</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59550</t>
+          <t>58556</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3294</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7455</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5167</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1638</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2969</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356110</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356110</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356110</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
